--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -522,7 +522,7 @@
         <v>57.9</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>43.36</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="4">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:40</t>
+    <t xml:space="preserve">2026-10-05 04:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -575,7 +575,7 @@
         <v>-15.51</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>44.03</v>
+        <v>44.04</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>59.55</v>
@@ -603,7 +603,7 @@
         <v>-27.09</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>64.92</v>
+        <v>64.93</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>92.02</v>
